--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.40961444660025</v>
+        <v>4.616562347572541</v>
       </c>
       <c r="D2" t="n">
-        <v>29.38427215807537</v>
+        <v>4.774944225687247</v>
       </c>
       <c r="E2" t="n">
-        <v>15.25299901269029</v>
+        <v>2.478612339562172</v>
       </c>
       <c r="F2" t="n">
-        <v>15.01436547072441</v>
+        <v>2.439834388992717</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.8092777718181</v>
+        <v>7.119007637920441</v>
       </c>
       <c r="D3" t="n">
-        <v>42.70269773949929</v>
+        <v>6.939188382668635</v>
       </c>
       <c r="E3" t="n">
-        <v>15.25299901269029</v>
+        <v>2.478612339562172</v>
       </c>
       <c r="F3" t="n">
-        <v>15.01436547072441</v>
+        <v>2.439834388992717</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.58962049925552</v>
+        <v>10.65831333112902</v>
       </c>
       <c r="D4" t="n">
-        <v>65.73194941265311</v>
+        <v>10.68144177955613</v>
       </c>
       <c r="E4" t="n">
-        <v>15.25299901269029</v>
+        <v>2.478612339562172</v>
       </c>
       <c r="F4" t="n">
-        <v>15.01436547072441</v>
+        <v>2.439834388992717</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
